--- a/artfynd/A 56857-2023 artfynd.xlsx
+++ b/artfynd/A 56857-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56857-2023 artfynd.xlsx
+++ b/artfynd/A 56857-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113335261</v>
+        <v>113335172</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574752</v>
+        <v>574615</v>
       </c>
       <c r="R2" t="n">
-        <v>6420492</v>
+        <v>6420455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113335314</v>
+        <v>113335201</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -838,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574819</v>
+        <v>574703</v>
       </c>
       <c r="R3" t="n">
-        <v>6420527</v>
+        <v>6420484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113335305</v>
+        <v>113335219</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574825</v>
+        <v>574710</v>
       </c>
       <c r="R4" t="n">
-        <v>6420518</v>
+        <v>6420475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113335354</v>
+        <v>113335232</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,11 +1033,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1068,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574715</v>
+        <v>574730</v>
       </c>
       <c r="R5" t="n">
-        <v>6420676</v>
+        <v>6420486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113335232</v>
+        <v>113335244</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1139,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1179,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574730</v>
+        <v>574740</v>
       </c>
       <c r="R6" t="n">
-        <v>6420486</v>
+        <v>6420487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113335219</v>
+        <v>113335254</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1251,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1294,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574710</v>
+        <v>574750</v>
       </c>
       <c r="R7" t="n">
-        <v>6420475</v>
+        <v>6420477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113335244</v>
+        <v>113335261</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,11 +1359,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1409,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574740</v>
+        <v>574752</v>
       </c>
       <c r="R8" t="n">
-        <v>6420487</v>
+        <v>6420492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,12 +1440,7 @@
         <v>113335272</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113335332</v>
+        <v>113335305</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574817</v>
+        <v>574825</v>
       </c>
       <c r="R10" t="n">
-        <v>6420557</v>
+        <v>6420518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,15 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113335381</v>
+        <v>113335314</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,7 +1685,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1750,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574584</v>
+        <v>574819</v>
       </c>
       <c r="R11" t="n">
-        <v>6420630</v>
+        <v>6420527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,15 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113335172</v>
+        <v>113335332</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1797,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1865,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574615</v>
+        <v>574817</v>
       </c>
       <c r="R12" t="n">
-        <v>6420455</v>
+        <v>6420557</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,15 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113335254</v>
+        <v>113335354</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1907,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1980,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574750</v>
+        <v>574715</v>
       </c>
       <c r="R13" t="n">
-        <v>6420477</v>
+        <v>6420676</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,15 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113335201</v>
+        <v>113335381</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,11 +2015,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2095,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574703</v>
+        <v>574584</v>
       </c>
       <c r="R14" t="n">
-        <v>6420484</v>
+        <v>6420630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,12 +2096,7 @@
         <v>113335342</v>
       </c>
       <c r="B15" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
